--- a/Archivo-Publicacion.xlsx
+++ b/Archivo-Publicacion.xlsx
@@ -828,10 +828,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G999"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.01"/>
   </cols>
   <sheetData>
@@ -866,247 +866,94 @@
       <c r="E3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>3238572</v>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>3240890</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>3251613</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="6"/>
       <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>3239247</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>3251615</v>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>3240892</v>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>3240887</v>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>3251623</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>3240889</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>3251621</v>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>3238372</v>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>3251612</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>3239219</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>3251620</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>3240888</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>3251627</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>3238132</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>3239221</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>3238133</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>3238135</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>3251614</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>3239223</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>5993</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1"/>
@@ -5019,7 +4866,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" id="{9CB474FB-7BF6-49EB-8643-4EBEABA0BD31}">
+          <x14:cfRule type="expression" priority="2" id="{19F67072-D523-4B22-AE2F-9B30CA3DC0AF}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5043,7 +4890,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="3" id="{D7156630-14EA-4AEE-815F-E2178D986516}">
+          <x14:cfRule type="expression" priority="3" id="{F7304F80-E481-43DB-B5D5-6B388790656D}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5063,7 +4910,7 @@
           <xm:sqref>A3 C189:C2556 C3 C155 C157 C159 C161 C163 C165 C167 C169 C171 C173 C175 C177 C179 C181 C183 C185 C187 C5 C43 C45 C47 C49 C51 C53 C55 C57 C59 C61 C63 C65 C67 C69 C71 C73 C75 C77 C79 C81 C83 C85 C87 C89 C91 C93 C95 C97 C99 C101 C103 C105 C107 C109 C111 C113 C115 C117 C119 C121 C123 C125 C127 C129 C131 C133 C135 C137 C139 C141 C143 C145 C147 C149 C151 C153 C27 C29 C31 C33 C35 C37 C39 C41 C7 C9 C11 C13 C15 C17 C19 C21 C23 C25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="4" id="{166B1E2B-29DC-456A-9A76-7D64AC7D3098}">
+          <x14:cfRule type="expression" priority="4" id="{AEEC6C19-D99C-4D15-B634-A4C75573884B}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5087,7 +4934,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="5" id="{7593825D-6C35-4480-BD5B-431DC2F9A051}">
+          <x14:cfRule type="expression" priority="5" id="{F2698415-2513-4017-A2BE-BECA8BFB501B}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5107,7 +4954,7 @@
           <xm:sqref>C189:C2556 C155 C157 C159 C161 C163 C165 C167 C169 C171 C173 C175 C177 C179 C181 C183 C185 C187 C5 C43 C45 C47 C49 C51 C53 C55 C57 C59 C61 C63 C65 C67 C69 C71 C73 C75 C77 C79 C81 C83 C85 C87 C89 C91 C93 C95 C97 C99 C101 C103 C105 C107 C109 C111 C113 C115 C117 C119 C121 C123 C125 C127 C129 C131 C133 C135 C137 C139 C141 C143 C145 C147 C149 C151 C153 C27 C29 C31 C33 C35 C37 C39 C41 C7 C9 C11 C13 C15 C17 C19 C21 C23 C25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="6" id="{3659CD7D-5F24-4772-ABC9-2734D4A999A0}">
+          <x14:cfRule type="expression" priority="6" id="{CDDD54D5-AFBC-48CD-B170-7FCE35B8C6A3}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5131,7 +4978,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="7" id="{746586A0-413F-443D-AFA1-C0A8C5F69A4B}">
+          <x14:cfRule type="expression" priority="7" id="{54E523DB-BD59-40D3-81BE-D5BF748EF4A1}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5151,7 +4998,7 @@
           <xm:sqref>C10590:C11186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="8" id="{D026C079-751E-45B0-B4AB-3F31714A10C9}">
+          <x14:cfRule type="expression" priority="8" id="{70AC3BA3-298C-4CDC-831B-BAFEF7FD65C1}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5175,7 +5022,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="9" id="{8A38F322-C025-4A3B-9924-8A4529B68146}">
+          <x14:cfRule type="expression" priority="9" id="{989A4DEF-9E2B-44F3-B819-BFC5917CB420}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5195,7 +5042,7 @@
           <xm:sqref>C5809:C9997</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="10" id="{6BEEF066-4077-4044-AAC6-A0C543885B61}">
+          <x14:cfRule type="expression" priority="10" id="{C45CB390-B25A-4545-9C69-13BFDB6AE2E0}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5219,7 +5066,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="11" id="{687BC7A6-40BA-443C-90B7-EBADB72A128D}">
+          <x14:cfRule type="expression" priority="11" id="{529F5825-1786-4D93-B997-4E62811C3A44}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5236,7 +5083,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="12" id="{8FE0A53E-BE61-4453-84CC-D3193A83E81D}">
+          <x14:cfRule type="expression" priority="12" id="{B765D5D9-CBC1-4BD2-ACD1-6F8EBC72C6CD}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5260,7 +5107,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="13" id="{603431BE-8F81-4863-93D7-2ACCF1BCE0DF}">
+          <x14:cfRule type="expression" priority="13" id="{A0927791-CE76-4BFF-9415-347EB4F112A8}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5280,7 +5127,7 @@
           <xm:sqref>C9998:C10589</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="14" id="{8C7848A0-B0E2-40A1-81E0-2BDE4D84DD3D}">
+          <x14:cfRule type="expression" priority="14" id="{9AA8EDFC-28EE-4332-8DD7-173815E692A8}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5304,7 +5151,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="15" id="{1FD7DB92-ECCF-4EC8-B9D7-AB12D6CCAA7B}">
+          <x14:cfRule type="expression" priority="15" id="{2CD65732-E264-4955-AE27-321D61A056E5}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5321,7 +5168,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="16" id="{F00039C5-4290-4573-B842-D78ADEA26E81}">
+          <x14:cfRule type="expression" priority="16" id="{B7125A86-FDC7-4718-B170-20CFE8D3D695}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5345,7 +5192,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="17" id="{AE59FB3E-1A38-401F-9B23-22906D479B40}">
+          <x14:cfRule type="expression" priority="17" id="{9395F677-E44D-4836-A755-677421542520}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5365,7 +5212,7 @@
           <xm:sqref>C189:C5808 C155 C157 C159 C161 C163 C165 C167 C169 C171 C173 C175 C177 C179 C181 C183 C185 C187 C5 C43 C45 C47 C49 C51 C53 C55 C57 C59 C61 C63 C65 C67 C69 C71 C73 C75 C77 C79 C81 C83 C85 C87 C89 C91 C93 C95 C97 C99 C101 C103 C105 C107 C109 C111 C113 C115 C117 C119 C121 C123 C125 C127 C129 C131 C133 C135 C137 C139 C141 C143 C145 C147 C149 C151 C153 C27 C29 C31 C33 C35 C37 C39 C41 C7 C9 C11 C13 C15 C17 C19 C21 C23 C25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="18" id="{2AAD9B26-92D0-4269-8FA0-1FEDA047BACC}">
+          <x14:cfRule type="expression" priority="18" id="{2B2FF880-C3AB-46B5-9239-69CE928046EA}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5389,7 +5236,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="19" id="{D511B33D-55C8-4990-83F7-25158C569EB9}">
+          <x14:cfRule type="expression" priority="19" id="{12A6FC33-9450-497B-BE3A-268F4B11FECF}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5406,7 +5253,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="20" id="{ED5A6BBB-14C4-4384-A8D0-41E8CAF8FAA7}">
+          <x14:cfRule type="expression" priority="20" id="{723B207E-D52B-4DF0-9A49-2D686DFA256F}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5430,7 +5277,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="21" id="{ECE4C4B6-7E85-4A1B-8E75-2086316C92A1}">
+          <x14:cfRule type="expression" priority="21" id="{BC67FB14-6A30-44A2-9283-30867DE8C8A2}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5450,7 +5297,7 @@
           <xm:sqref>C4:C189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="22" id="{7F75E269-12AE-49E2-85F0-B35DA7C5DA6D}">
+          <x14:cfRule type="expression" priority="22" id="{C43CC913-BB10-483C-80B3-E0D5A62F6260}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5474,7 +5321,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="23" id="{52FF2AD7-BB30-467D-9D30-FCCE1A201F82}">
+          <x14:cfRule type="expression" priority="23" id="{AAEAFADB-76E6-45E6-99CA-E02468E94FCA}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5491,7 +5338,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="24" id="{49123767-CF5A-414C-A38C-A0FABF49FC90}">
+          <x14:cfRule type="expression" priority="24" id="{F7A71CC5-9757-48C0-ABA2-7277E4B18F42}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="REQUIRED",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5515,7 +5362,7 @@
               </border>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="25" id="{48653CC0-85B2-4AB4-84D1-306EE5EA48E0}">
+          <x14:cfRule type="expression" priority="25" id="{9BF628E6-9649-4BAA-A37D-8A8A40D2B24E}">
             <xm:f>IF(INDEX(OFFSET(Columns!$A$1,1,2,15,1),MATCH(INDIRECT(ADDRESS(5,COLUMN())),Columns!$A$2:$A$15,0),MATCH(INDIRECT(ADDRESS(ROW(),1)),OFFSET(Columns!$A$1,0,2,1,1),0))="N/A",1,0)</xm:f>
             <x14:dxf>
               <font>
@@ -5546,7 +5393,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -5727,7 +5574,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
